--- a/artfynd/A 4265-2026 artfynd.xlsx
+++ b/artfynd/A 4265-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>86375142</v>
+        <v>126556962</v>
       </c>
       <c r="B2" t="n">
-        <v>96237</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,53 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220093</v>
+        <v>100088</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Våtmark SV Björkön, Mpd</t>
+          <t>Hummelviken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631763.1142019966</v>
+        <v>631850</v>
       </c>
       <c r="R2" t="n">
-        <v>6902690.537653402</v>
+        <v>6902562</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-06-20</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-06-20</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,22 +773,266 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Kerstin Stickler</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Kerstin Stickler</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126556979</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57505</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100134</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skräntärna</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydroprogne caspia</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Pallas, 1770)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hummelviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>631850</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6902562</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Kerstin Stickler</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Kerstin Stickler</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>86375142</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Våtmark SV Björkön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>631763</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6902691</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-06-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-06-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Peter Nilsson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Peter Nilsson, Kerstin Stickler</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4265-2026 artfynd.xlsx
+++ b/artfynd/A 4265-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126556962</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126556979</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1033,8 +1048,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375142</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>